--- a/stacked_model/results/validation/monte_carlo_error_propagation/mc_error_propagation_summary.xlsx
+++ b/stacked_model/results/validation/monte_carlo_error_propagation/mc_error_propagation_summary.xlsx
@@ -558,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="N2" t="n">
         <v>2000</v>
@@ -599,25 +599,25 @@
         <v>50</v>
       </c>
       <c r="P2" t="n">
-        <v>2.578108664189561</v>
+        <v>2.569077111832257</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3927313737468845</v>
+        <v>0.3604821945638521</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9203199013654335</v>
+        <v>0.9071567584119096</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2276390482372889</v>
+        <v>0.2020085945460311</v>
       </c>
       <c r="T2" t="n">
-        <v>1.213819151359073</v>
+        <v>1.191336901710597</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3054811908054664</v>
+        <v>0.2741209365172102</v>
       </c>
       <c r="V2" t="n">
-        <v>3.992483516794094</v>
+        <v>3.994914697570735</v>
       </c>
     </row>
   </sheetData>
